--- a/Data/g17.3.xlsx
+++ b/Data/g17.3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -586,6 +586,18 @@
         <v>23</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
